--- a/ISOC_result/Map3_9/Map3_9_result.xlsx
+++ b/ISOC_result/Map3_9/Map3_9_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ISOC\ISOC_result\Map3_9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA49CB8-39B1-4FB1-8999-00E9D7A4A412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F3BDCD-8092-4823-853E-01CF4BE55C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8F062009-FD71-4F10-8C79-40340D4D7484}"/>
   </bookViews>
@@ -951,7 +951,7 @@
         <v>7043.67</v>
       </c>
       <c r="D22" s="2">
-        <v>3486.82</v>
+        <v>640.78</v>
       </c>
       <c r="E22" s="2">
         <v>56720</v>
